--- a/ContabilidadeFinanceira/Treinos/Ex3_ValeVerde.xlsx
+++ b/ContabilidadeFinanceira/Treinos/Ex3_ValeVerde.xlsx
@@ -44,14 +44,14 @@
       <b val="1"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <b val="1"/>
       <i val="1"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -120,28 +120,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -522,17 +524,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,14 +550,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Uma linha por movimento. Se a transação mexe em duas contas do mesmo lado (ex: sai caixa, entra estoque), usa as duas linhas.</t>
+          <t>Uma linha por movimento: escreve a conta e o valor, com sinal. Transação que mexe em três contas do mesmo lado usa as três linhas. A coluna Check acusa se aquela transação fechou.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Transação</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -565,395 +570,510 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>PASSIVO</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Recebimento de R$ 12.000 de clientes, referente a vendas do mês anterior</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="8">
-        <f>IF(COUNT(C5:C6,E5:E6,G5:G6)=0,"",IF(SUM(C5:C6)-SUM(E5:E6)-SUM(G5:G6)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="6">
+        <f>IF(COUNT(D6:D7,G6:G7,J6:J7)=0,"",IF(SUM(D6:D7)-SUM(G6:G7)-SUM(J6:J7)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Compra de mercadorias por R$ 40.000, integralmente a prazo</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="8">
-        <f>IF(COUNT(C7:C8,E7:E8,G7:G8)=0,"",IF(SUM(C7:C8)-SUM(E7:E8)-SUM(G7:G8)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="6">
+        <f>IF(COUNT(D8:D9,G8:G9,J8:J9)=0,"",IF(SUM(D8:D9)-SUM(G8:G9)-SUM(J8:J9)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Venda de mercadorias por R$ 65.000 (R$ 40.000 à vista, R$ 25.000 a prazo); custo de R$ 45.000</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="8">
-        <f>IF(COUNT(C9:C10,E9:E10,G9:G10)=0,"",IF(SUM(C9:C10)-SUM(E9:E10)-SUM(G9:G10)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="6">
+        <f>IF(COUNT(D10:D12,G10:G12,J10:J12)=0,"",IF(SUM(D10:D12)-SUM(G10:G12)-SUM(J10:J12)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Compra de veículo de entrega por R$ 36.000: R$ 6.000 de entrada e o restante a prazo</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8">
-        <f>IF(COUNT(C11:C12,E11:E12,G11:G12)=0,"",IF(SUM(C11:C12)-SUM(E11:E12)-SUM(G11:G12)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="6">
+        <f>IF(COUNT(D13:D14,G13:G14,J13:J14)=0,"",IF(SUM(D13:D14)-SUM(G13:G14)-SUM(J13:J14)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Pagamento de R$ 38.000 a fornecedores</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8">
-        <f>IF(COUNT(C13:C14,E13:E14,G13:G14)=0,"",IF(SUM(C13:C14)-SUM(E13:E14)-SUM(G13:G14)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="6">
+        <f>IF(COUNT(D15:D16,G15:G16,J15:J16)=0,"",IF(SUM(D15:D16)-SUM(G15:G16)-SUM(J15:J16)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Pagamento à vista de despesas de vendas e administrativas: R$ 14.000</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="8">
-        <f>IF(COUNT(C15:C16,E15:E16,G15:G16)=0,"",IF(SUM(C15:C16)-SUM(E15:E16)-SUM(G15:G16)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="6">
+        <f>IF(COUNT(D17:D18,G17:G18,J17:J18)=0,"",IF(SUM(D17:D18)-SUM(G17:G18)-SUM(J17:J18)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Aporte adicional de capital dos sócios: R$ 20.000 em dinheiro</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="8">
-        <f>IF(COUNT(C17:C18,E17:E18,G17:G18)=0,"",IF(SUM(C17:C18)-SUM(E17:E18)-SUM(G17:G18)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="6">
+        <f>IF(COUNT(D19:D20,G19:G20,J19:J20)=0,"",IF(SUM(D19:D20)-SUM(G19:G20)-SUM(J19:J20)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Distribuição de dividendos de R$ 5.000 em dinheiro</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="8">
-        <f>IF(COUNT(C19:C20,E19:E20,G19:G20)=0,"",IF(SUM(C19:C20)-SUM(E19:E20)-SUM(G19:G20)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="6">
+        <f>IF(COUNT(D21:D22,G21:G22,J21:J22)=0,"",IF(SUM(D21:D22)-SUM(G21:G22)-SUM(J21:J22)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="H9:H10"/>
+  <mergeCells count="27">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K21:K22"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="K10:K12"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A8:A9"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K17:K18"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="B21:B22"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Caixa,Contas a Receber,Estoque,Imobilizado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Contas a Pagar"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Capital Social,Lucros Acumulados"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -989,61 +1109,61 @@
           <t>Distribuidora Vale Verde  |  Mês 2  |  valores em R$</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Transações, por Número e Descrição</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Recebimento de R$ 12.000 de clientes, referente a vendas do </t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Compra de mercadorias por R$ 40.000, integralmente a prazo</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Venda de mercadorias por R$ 65.000 (R$ 40.000 à vista, R$ 25</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Compra de veículo de entrega por R$ 36.000: R$ 6.000 de entr</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Pagamento de R$ 38.000 a fornecedores</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Pagamento à vista de despesas de vendas e administrativas: R</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Aporte adicional de capital dos sócios: R$ 20.000 em dinheir</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>Distribuição de dividendos de R$ 5.000 em dinheiro</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Balanço Patrimonial</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Balanço Inicial</t>
         </is>
@@ -1072,21 +1192,21 @@
       <c r="K3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Balanço Final</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Ativo Circulante</t>
         </is>
@@ -1098,22 +1218,22 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="15">
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="17">
         <f>C6+SUM(D6:K6)</f>
         <v/>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="18">
         <f>IF(COUNT(D6:K6)=0,"",IF(ABS(L6-Gabarito!L6)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1124,22 +1244,22 @@
           <t>Contas a Receber</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="15">
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="17">
         <f>C7+SUM(D7:K7)</f>
         <v/>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="18">
         <f>IF(COUNT(D7:K7)=0,"",IF(ABS(L7-Gabarito!L7)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1150,28 +1270,28 @@
           <t>Estoque</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="15">
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="17">
         <f>C8+SUM(D8:K8)</f>
         <v/>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="18">
         <f>IF(COUNT(D8:K8)=0,"",IF(ABS(L8-Gabarito!L8)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Ativo Não Circulante</t>
         </is>
@@ -1183,82 +1303,82 @@
           <t>Imobilizado</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="16" t="n">
         <v>50000</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="15">
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="17">
         <f>C10+SUM(D10:K10)</f>
         <v/>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="18">
         <f>IF(COUNT(D10:K10)=0,"",IF(ABS(L10-Gabarito!L10)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total do Ativo</t>
         </is>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="20">
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="20">
         <f>SUM(D6:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="20">
         <f>SUM(E6:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="20">
         <f>SUM(F6:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="20">
         <f>SUM(G6:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>SUM(H6:H10)</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="20">
         <f>SUM(I6:I10)</f>
         <v/>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="20">
         <f>SUM(J6:J10)</f>
         <v/>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="20">
         <f>SUM(K6:K10)</f>
         <v/>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="20">
         <f>SUM(L6:L10)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>PASSIVO E PATRIM. LÍQUIDO</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Passivo Circulante:</t>
         </is>
@@ -1270,28 +1390,28 @@
           <t>Contas a Pagar</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="15">
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="17">
         <f>C14+SUM(D14:K14)</f>
         <v/>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="18">
         <f>IF(COUNT(D14:K14)=0,"",IF(ABS(L14-Gabarito!L14)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Patrimônio Líquido:</t>
         </is>
@@ -1303,22 +1423,22 @@
           <t>Capital Social</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="16" t="n">
         <v>70000</v>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="15">
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="17">
         <f>C16+SUM(D16:K16)</f>
         <v/>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="18">
         <f>IF(COUNT(D16:K16)=0,"",IF(ABS(L16-Gabarito!L16)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1329,126 +1449,126 @@
           <t>Lucros Acumulados</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="15">
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="17">
         <f>C17+SUM(D17:K17)</f>
         <v/>
       </c>
-      <c r="N17" s="16">
+      <c r="N17" s="18">
         <f>IF(COUNT(D17:K17)=0,"",IF(ABS(L17-Gabarito!L17)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Total Passivo e Patrim. Líquido</t>
         </is>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="20">
         <f>SUM(C13:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <f>SUM(D13:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="20">
         <f>SUM(E13:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="20">
         <f>SUM(F13:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="20">
         <f>SUM(G13:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="20">
         <f>SUM(H13:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="20">
         <f>SUM(I13:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="20">
         <f>SUM(J13:J17)</f>
         <v/>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="20">
         <f>SUM(K13:K17)</f>
         <v/>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="20">
         <f>SUM(L13:L17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Diferença, se houver (tem que dar zero)</t>
         </is>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="17">
         <f>C11-C18</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="17">
         <f>D11-D18</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="17">
         <f>E11-E18</f>
         <v/>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="17">
         <f>F11-F18</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="17">
         <f>G11-G18</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="17">
         <f>H11-H18</f>
         <v/>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="17">
         <f>I11-I18</f>
         <v/>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="17">
         <f>J11-J18</f>
         <v/>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="17">
         <f>K11-K18</f>
         <v/>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="17">
         <f>L11-L18</f>
         <v/>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="19">
         <f>IF(L20=0,"✔ fecha","✗ não fecha")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Demonstração do Resultado</t>
         </is>
@@ -1477,12 +1597,12 @@
       <c r="K22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="13" t="inlineStr">
         <is>
           <t>Mês 2</t>
         </is>
       </c>
-      <c r="N22" s="20" t="inlineStr">
+      <c r="N22" s="22" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -1494,19 +1614,19 @@
           <t>Receita de Vendas</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="15">
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="17">
         <f>SUM(D23:K23)</f>
         <v/>
       </c>
-      <c r="N23" s="16">
+      <c r="N23" s="18">
         <f>IF(COUNT(D23:K23)=0,"",IF(ABS(L23-Gabarito!L23)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1517,62 +1637,62 @@
           <t>(-) Custo das Mercadorias Vendidas</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="15">
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="17">
         <f>SUM(D24:K24)</f>
         <v/>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="18">
         <f>IF(COUNT(D24:K24)=0,"",IF(ABS(L24-Gabarito!L24)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) Lucro Bruto</t>
         </is>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="20">
         <f>SUM(D23:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="20">
         <f>SUM(E23:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="20">
         <f>SUM(F23:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="20">
         <f>SUM(G23:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="20">
         <f>SUM(H23:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="20">
         <f>SUM(I23:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="20">
         <f>SUM(J23:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="20">
         <f>SUM(K23:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="18">
+      <c r="L25" s="20">
         <f>SUM(L23:L24)</f>
         <v/>
       </c>
@@ -1583,68 +1703,68 @@
           <t>(-) Despesas Operacionais</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="15">
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="17">
         <f>SUM(D26:K26)</f>
         <v/>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="18">
         <f>IF(COUNT(D26:K26)=0,"",IF(ABS(L26-Gabarito!L26)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) EBIT e Lucro Líquido</t>
         </is>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="20">
         <f>SUM(D25:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="20">
         <f>SUM(E25:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="20">
         <f>SUM(F25:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="20">
         <f>SUM(G25:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="20">
         <f>SUM(H25:H26)</f>
         <v/>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="20">
         <f>SUM(I25:I26)</f>
         <v/>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="20">
         <f>SUM(J25:J26)</f>
         <v/>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="20">
         <f>SUM(K25:K26)</f>
         <v/>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="20">
         <f>SUM(L25:L26)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Demonstração dos Fluxos de Caixa</t>
         </is>
@@ -1673,51 +1793,51 @@
       <c r="K29" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>Mês 2</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>OPERAÇÕES</t>
         </is>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="20">
         <f>SUM(D31:D33)</f>
         <v/>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="20">
         <f>SUM(E31:E33)</f>
         <v/>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="20">
         <f>SUM(F31:F33)</f>
         <v/>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="20">
         <f>SUM(G31:G33)</f>
         <v/>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="20">
         <f>SUM(H31:H33)</f>
         <v/>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="20">
         <f>SUM(I31:I33)</f>
         <v/>
       </c>
-      <c r="J30" s="18">
+      <c r="J30" s="20">
         <f>SUM(J31:J33)</f>
         <v/>
       </c>
-      <c r="K30" s="18">
+      <c r="K30" s="20">
         <f>SUM(K31:K33)</f>
         <v/>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="20">
         <f>SUM(L31:L33)</f>
         <v/>
       </c>
@@ -1728,19 +1848,19 @@
           <t>Recebimentos de Clientes</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="15">
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="17">
         <f>SUM(D31:K31)</f>
         <v/>
       </c>
-      <c r="N31" s="16">
+      <c r="N31" s="18">
         <f>IF(COUNT(D31:K31)=0,"",IF(ABS(L31-Gabarito!L31)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1751,19 +1871,19 @@
           <t>Pagamentos a Fornecedores</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="15">
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="17">
         <f>SUM(D32:K32)</f>
         <v/>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="18">
         <f>IF(COUNT(D32:K32)=0,"",IF(ABS(L32-Gabarito!L32)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1774,62 +1894,62 @@
           <t>Pagamentos de Despesas</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="15">
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="17">
         <f>SUM(D33:K33)</f>
         <v/>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="18">
         <f>IF(COUNT(D33:K33)=0,"",IF(ABS(L33-Gabarito!L33)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>INVESTIMENTOS</t>
         </is>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="20">
         <f>SUM(D35:D35)</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="20">
         <f>SUM(E35:E35)</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="20">
         <f>SUM(F35:F35)</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="20">
         <f>SUM(G35:G35)</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>SUM(H35:H35)</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="20">
         <f>SUM(I35:I35)</f>
         <v/>
       </c>
-      <c r="J34" s="18">
+      <c r="J34" s="20">
         <f>SUM(J35:J35)</f>
         <v/>
       </c>
-      <c r="K34" s="18">
+      <c r="K34" s="20">
         <f>SUM(K35:K35)</f>
         <v/>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="20">
         <f>SUM(L35:L35)</f>
         <v/>
       </c>
@@ -1840,62 +1960,62 @@
           <t>Aquisição de Imobilizado</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="15">
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="17">
         <f>SUM(D35:K35)</f>
         <v/>
       </c>
-      <c r="N35" s="16">
+      <c r="N35" s="18">
         <f>IF(COUNT(D35:K35)=0,"",IF(ABS(L35-Gabarito!L35)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>FINANCIAMENTOS</t>
         </is>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="20">
         <f>SUM(D37:D38)</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="20">
         <f>SUM(E37:E38)</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="20">
         <f>SUM(F37:F38)</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="20">
         <f>SUM(G37:G38)</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>SUM(H37:H38)</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="20">
         <f>SUM(I37:I38)</f>
         <v/>
       </c>
-      <c r="J36" s="18">
+      <c r="J36" s="20">
         <f>SUM(J37:J38)</f>
         <v/>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="20">
         <f>SUM(K37:K38)</f>
         <v/>
       </c>
-      <c r="L36" s="18">
+      <c r="L36" s="20">
         <f>SUM(L37:L38)</f>
         <v/>
       </c>
@@ -1906,19 +2026,19 @@
           <t>Ingresso de Capital</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="15">
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="17">
         <f>SUM(D37:K37)</f>
         <v/>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="18">
         <f>IF(COUNT(D37:K37)=0,"",IF(ABS(L37-Gabarito!L37)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
@@ -1929,62 +2049,62 @@
           <t>Dividendos Pagos</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="15">
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="17">
         <f>SUM(D38:K38)</f>
         <v/>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="18">
         <f>IF(COUNT(D38:K38)=0,"",IF(ABS(L38-Gabarito!L38)&lt;0.5,"✔","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>VARIAÇÃO NO CAIXA</t>
         </is>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="20">
         <f>D30+D34+D36</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="20">
         <f>E30+E34+E36</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="20">
         <f>F30+F34+F36</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="20">
         <f>G30+G34+G36</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="20">
         <f>H30+H34+H36</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="20">
         <f>I30+I34+I36</f>
         <v/>
       </c>
-      <c r="J39" s="18">
+      <c r="J39" s="20">
         <f>J30+J34+J36</f>
         <v/>
       </c>
-      <c r="K39" s="18">
+      <c r="K39" s="20">
         <f>K30+K34+K36</f>
         <v/>
       </c>
-      <c r="L39" s="18">
+      <c r="L39" s="20">
         <f>L30+L34+L36</f>
         <v/>
       </c>
@@ -1995,38 +2115,38 @@
           <t xml:space="preserve">    Saldo inicial de caixa</t>
         </is>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="L40" s="16" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    Saldo final de caixa</t>
         </is>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="17">
         <f>L40+L39</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Caixa final da DFC menos Caixa do BP (tem que dar zero)</t>
         </is>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="17">
         <f>L41-L6</f>
         <v/>
       </c>
-      <c r="N43" s="17">
+      <c r="N43" s="19">
         <f>IF(L43=0,"✔ amarra","✗ não amarra")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Indicadores (automáticos)</t>
         </is>
@@ -2038,7 +2158,7 @@
           <t>Margem bruta</t>
         </is>
       </c>
-      <c r="L46" s="21">
+      <c r="L46" s="23">
         <f>IF(L23=0,"",L25/L23)</f>
         <v/>
       </c>
@@ -2049,7 +2169,7 @@
           <t>Margem líquida</t>
         </is>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="23">
         <f>IF(L23=0,"",L27/L23)</f>
         <v/>
       </c>
@@ -2060,7 +2180,7 @@
           <t>% financiado por capital próprio (PL / Ativo)</t>
         </is>
       </c>
-      <c r="L48" s="21">
+      <c r="L48" s="23">
         <f>IF(L11=0,"",SUM(L16:L17)/L11)</f>
         <v/>
       </c>
@@ -2071,7 +2191,7 @@
           <t>ROE (LL / PL final)</t>
         </is>
       </c>
-      <c r="L49" s="21">
+      <c r="L49" s="23">
         <f>IF(SUM(L16:L17)=0,"",L27/SUM(L16:L17))</f>
         <v/>
       </c>
@@ -2112,61 +2232,61 @@
           <t>Distribuidora Vale Verde  |  Mês 2  |  valores em R$</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Transações, por Número e Descrição</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Recebimento de R$ 12.000 de clientes, referente a vendas do </t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Compra de mercadorias por R$ 40.000, integralmente a prazo</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Venda de mercadorias por R$ 65.000 (R$ 40.000 à vista, R$ 25</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Compra de veículo de entrega por R$ 36.000: R$ 6.000 de entr</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Pagamento de R$ 38.000 a fornecedores</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Pagamento à vista de despesas de vendas e administrativas: R</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Aporte adicional de capital dos sócios: R$ 20.000 em dinheir</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>Distribuição de dividendos de R$ 5.000 em dinheiro</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Balanço Patrimonial</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Balanço Inicial</t>
         </is>
@@ -2195,21 +2315,21 @@
       <c r="K3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Balanço Final</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Ativo Circulante</t>
         </is>
@@ -2221,32 +2341,32 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="9" t="n">
         <v>12000</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>-6000</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-38000</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>-5000</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="17">
         <f>C6+SUM(D6:K6)</f>
         <v/>
       </c>
@@ -2257,22 +2377,22 @@
           <t>Contas a Receber</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="9" t="n">
         <v>-12000</v>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n">
         <v>25000</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="15">
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="17">
         <f>C7+SUM(D7:K7)</f>
         <v/>
       </c>
@@ -2283,28 +2403,28 @@
           <t>Estoque</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n">
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-45000</v>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="15">
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="17">
         <f>C8+SUM(D8:K8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Ativo Não Circulante</t>
         </is>
@@ -2316,80 +2436,80 @@
           <t>Imobilizado</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="16" t="n">
         <v>50000</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n">
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="15">
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="17">
         <f>C10+SUM(D10:K10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total do Ativo</t>
         </is>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="20">
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="20">
         <f>SUM(D6:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="20">
         <f>SUM(E6:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="20">
         <f>SUM(F6:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="20">
         <f>SUM(G6:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>SUM(H6:H10)</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="20">
         <f>SUM(I6:I10)</f>
         <v/>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="20">
         <f>SUM(J6:J10)</f>
         <v/>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="20">
         <f>SUM(K6:K10)</f>
         <v/>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="20">
         <f>SUM(L6:L10)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>PASSIVO E PATRIM. LÍQUIDO</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Passivo Circulante:</t>
         </is>
@@ -2401,30 +2521,30 @@
           <t>Contas a Pagar</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n">
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n">
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-38000</v>
       </c>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="15">
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="17">
         <f>C14+SUM(D14:K14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Patrimônio Líquido:</t>
         </is>
@@ -2436,20 +2556,20 @@
           <t>Capital Social</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="16" t="n">
         <v>70000</v>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n">
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="15">
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="17">
         <f>C16+SUM(D16:K16)</f>
         <v/>
       </c>
@@ -2460,124 +2580,124 @@
           <t>Lucros Acumulados</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n">
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n">
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n">
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n">
         <v>-5000</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="17">
         <f>C17+SUM(D17:K17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Total Passivo e Patrim. Líquido</t>
         </is>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="20">
         <f>SUM(C13:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <f>SUM(D13:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="20">
         <f>SUM(E13:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="20">
         <f>SUM(F13:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="20">
         <f>SUM(G13:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="20">
         <f>SUM(H13:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="20">
         <f>SUM(I13:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="20">
         <f>SUM(J13:J17)</f>
         <v/>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="20">
         <f>SUM(K13:K17)</f>
         <v/>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="20">
         <f>SUM(L13:L17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Diferença, se houver (tem que dar zero)</t>
         </is>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="17">
         <f>C11-C18</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="17">
         <f>D11-D18</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="17">
         <f>E11-E18</f>
         <v/>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="17">
         <f>F11-F18</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="17">
         <f>G11-G18</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="17">
         <f>H11-H18</f>
         <v/>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="17">
         <f>I11-I18</f>
         <v/>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="17">
         <f>J11-J18</f>
         <v/>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="17">
         <f>K11-K18</f>
         <v/>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="17">
         <f>L11-L18</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Demonstração do Resultado</t>
         </is>
@@ -2606,12 +2726,12 @@
       <c r="K22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="13" t="inlineStr">
         <is>
           <t>Mês 2</t>
         </is>
       </c>
-      <c r="N22" s="20" t="inlineStr">
+      <c r="N22" s="22" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -2623,17 +2743,17 @@
           <t>Receita de Vendas</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n">
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n">
         <v>65000</v>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="15">
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="17">
         <f>SUM(D23:K23)</f>
         <v/>
       </c>
@@ -2644,60 +2764,60 @@
           <t>(-) Custo das Mercadorias Vendidas</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n">
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n">
         <v>-45000</v>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="15">
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="17">
         <f>SUM(D24:K24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) Lucro Bruto</t>
         </is>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="20">
         <f>SUM(D23:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="20">
         <f>SUM(E23:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="20">
         <f>SUM(F23:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="20">
         <f>SUM(G23:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="20">
         <f>SUM(H23:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="20">
         <f>SUM(I23:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="20">
         <f>SUM(J23:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="20">
         <f>SUM(K23:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="18">
+      <c r="L25" s="20">
         <f>SUM(L23:L24)</f>
         <v/>
       </c>
@@ -2708,66 +2828,66 @@
           <t>(-) Despesas Operacionais</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n">
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="15">
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="17">
         <f>SUM(D26:K26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">     (=) EBIT e Lucro Líquido</t>
         </is>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="20">
         <f>SUM(D25:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="20">
         <f>SUM(E25:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="20">
         <f>SUM(F25:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="20">
         <f>SUM(G25:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="20">
         <f>SUM(H25:H26)</f>
         <v/>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="20">
         <f>SUM(I25:I26)</f>
         <v/>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="20">
         <f>SUM(J25:J26)</f>
         <v/>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="20">
         <f>SUM(K25:K26)</f>
         <v/>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="20">
         <f>SUM(L25:L26)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Demonstração dos Fluxos de Caixa</t>
         </is>
@@ -2796,51 +2916,51 @@
       <c r="K29" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>Mês 2</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>OPERAÇÕES</t>
         </is>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="20">
         <f>SUM(D31:D33)</f>
         <v/>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="20">
         <f>SUM(E31:E33)</f>
         <v/>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="20">
         <f>SUM(F31:F33)</f>
         <v/>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="20">
         <f>SUM(G31:G33)</f>
         <v/>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="20">
         <f>SUM(H31:H33)</f>
         <v/>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="20">
         <f>SUM(I31:I33)</f>
         <v/>
       </c>
-      <c r="J30" s="18">
+      <c r="J30" s="20">
         <f>SUM(J31:J33)</f>
         <v/>
       </c>
-      <c r="K30" s="18">
+      <c r="K30" s="20">
         <f>SUM(K31:K33)</f>
         <v/>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="20">
         <f>SUM(L31:L33)</f>
         <v/>
       </c>
@@ -2851,19 +2971,19 @@
           <t>Recebimentos de Clientes</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="9" t="n">
         <v>12000</v>
       </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n">
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="15">
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="17">
         <f>SUM(D31:K31)</f>
         <v/>
       </c>
@@ -2874,17 +2994,17 @@
           <t>Pagamentos a Fornecedores</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n">
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n">
         <v>-38000</v>
       </c>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="n"/>
-      <c r="L32" s="15">
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="17">
         <f>SUM(D32:K32)</f>
         <v/>
       </c>
@@ -2895,60 +3015,60 @@
           <t>Pagamentos de Despesas</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n">
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="15">
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="17">
         <f>SUM(D33:K33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>INVESTIMENTOS</t>
         </is>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="20">
         <f>SUM(D35:D35)</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="20">
         <f>SUM(E35:E35)</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="20">
         <f>SUM(F35:F35)</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="20">
         <f>SUM(G35:G35)</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="20">
         <f>SUM(H35:H35)</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="20">
         <f>SUM(I35:I35)</f>
         <v/>
       </c>
-      <c r="J34" s="18">
+      <c r="J34" s="20">
         <f>SUM(J35:J35)</f>
         <v/>
       </c>
-      <c r="K34" s="18">
+      <c r="K34" s="20">
         <f>SUM(K35:K35)</f>
         <v/>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="20">
         <f>SUM(L35:L35)</f>
         <v/>
       </c>
@@ -2959,60 +3079,60 @@
           <t>Aquisição de Imobilizado</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n">
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n">
         <v>-6000</v>
       </c>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="15">
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="17">
         <f>SUM(D35:K35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>FINANCIAMENTOS</t>
         </is>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="20">
         <f>SUM(D37:D38)</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="20">
         <f>SUM(E37:E38)</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="20">
         <f>SUM(F37:F38)</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="20">
         <f>SUM(G37:G38)</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="20">
         <f>SUM(H37:H38)</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="20">
         <f>SUM(I37:I38)</f>
         <v/>
       </c>
-      <c r="J36" s="18">
+      <c r="J36" s="20">
         <f>SUM(J37:J38)</f>
         <v/>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="20">
         <f>SUM(K37:K38)</f>
         <v/>
       </c>
-      <c r="L36" s="18">
+      <c r="L36" s="20">
         <f>SUM(L37:L38)</f>
         <v/>
       </c>
@@ -3023,17 +3143,17 @@
           <t>Ingresso de Capital</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n">
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="15">
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="17">
         <f>SUM(D37:K37)</f>
         <v/>
       </c>
@@ -3044,60 +3164,60 @@
           <t>Dividendos Pagos</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="n">
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n">
         <v>-5000</v>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="17">
         <f>SUM(D38:K38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>VARIAÇÃO NO CAIXA</t>
         </is>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="20">
         <f>D30+D34+D36</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="20">
         <f>E30+E34+E36</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="20">
         <f>F30+F34+F36</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="20">
         <f>G30+G34+G36</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="20">
         <f>H30+H34+H36</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="20">
         <f>I30+I34+I36</f>
         <v/>
       </c>
-      <c r="J39" s="18">
+      <c r="J39" s="20">
         <f>J30+J34+J36</f>
         <v/>
       </c>
-      <c r="K39" s="18">
+      <c r="K39" s="20">
         <f>K30+K34+K36</f>
         <v/>
       </c>
-      <c r="L39" s="18">
+      <c r="L39" s="20">
         <f>L30+L34+L36</f>
         <v/>
       </c>
@@ -3108,34 +3228,34 @@
           <t xml:space="preserve">    Saldo inicial de caixa</t>
         </is>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="L40" s="16" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    Saldo final de caixa</t>
         </is>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="17">
         <f>L40+L39</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Caixa final da DFC menos Caixa do BP (tem que dar zero)</t>
         </is>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="17">
         <f>L41-L6</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Indicadores (automáticos)</t>
         </is>
@@ -3147,7 +3267,7 @@
           <t>Margem bruta</t>
         </is>
       </c>
-      <c r="L46" s="21">
+      <c r="L46" s="23">
         <f>IF(L23=0,"",L25/L23)</f>
         <v/>
       </c>
@@ -3158,7 +3278,7 @@
           <t>Margem líquida</t>
         </is>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="23">
         <f>IF(L23=0,"",L27/L23)</f>
         <v/>
       </c>
@@ -3169,7 +3289,7 @@
           <t>% financiado por capital próprio (PL / Ativo)</t>
         </is>
       </c>
-      <c r="L48" s="21">
+      <c r="L48" s="23">
         <f>IF(L11=0,"",SUM(L16:L17)/L11)</f>
         <v/>
       </c>
@@ -3180,7 +3300,7 @@
           <t>ROE (LL / PL final)</t>
         </is>
       </c>
-      <c r="L49" s="21">
+      <c r="L49" s="23">
         <f>IF(SUM(L16:L17)=0,"",L27/SUM(L16:L17))</f>
         <v/>
       </c>
@@ -3196,17 +3316,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3219,14 +3342,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Uma linha por movimento. Se a transação mexe em duas contas do mesmo lado (ex: sai caixa, entra estoque), usa as duas linhas.</t>
+          <t>Uma linha por movimento: escreve a conta e o valor, com sinal. Transação que mexe em três contas do mesmo lado usa as três linhas. A coluna Check acusa se aquela transação fechou.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Transação</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3239,431 +3362,624 @@
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>PASSIVO</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>conta</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Recebimento de R$ 12.000 de clientes, referente a vendas do mês anterior</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>12000</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="8">
-        <f>IF(COUNT(C5:C6,E5:E6,G5:G6)=0,"",IF(SUM(C5:C6)-SUM(E5:E6)-SUM(G5:G6)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="6" t="n">
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="6">
+        <f>IF(COUNT(D6:D7,G6:G7,J6:J7)=0,"",IF(SUM(D6:D7)-SUM(G6:G7)-SUM(J6:J7)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Receber</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>-12000</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Compra de mercadorias por R$ 40.000, integralmente a prazo</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Estoque</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Pagar</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="8">
-        <f>IF(COUNT(C7:C8,E7:E8,G7:G8)=0,"",IF(SUM(C7:C8)-SUM(E7:E8)-SUM(G7:G8)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="6">
+        <f>IF(COUNT(D8:D9,G8:G9,J8:J9)=0,"",IF(SUM(D8:D9)-SUM(G8:G9)-SUM(J8:J9)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Venda de mercadorias por R$ 65.000 (R$ 40.000 à vista, R$ 25.000 a prazo); custo de R$ 45.000</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="H9" s="8">
-        <f>IF(COUNT(C9:C10,E9:E10,G9:G10)=0,"",IF(SUM(C9:C10)-SUM(E9:E10)-SUM(G9:G10)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="6" t="n">
+      <c r="K10" s="6">
+        <f>IF(COUNT(D10:D12,G10:G12,J10:J12)=0,"",IF(SUM(D10:D12)-SUM(G10:G12)-SUM(J10:J12)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Receber</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>25000</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Estoque</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>-45000</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Compra de veículo de entrega por R$ 36.000: R$ 6.000 de entrada e o restante a prazo</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>-6000</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Pagar</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="8">
-        <f>IF(COUNT(C11:C12,E11:E12,G11:G12)=0,"",IF(SUM(C11:C12)-SUM(E11:E12)-SUM(G11:G12)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="6" t="n">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="6">
+        <f>IF(COUNT(D13:D14,G13:G14,J13:J14)=0,"",IF(SUM(D13:D14)-SUM(G13:G14)-SUM(J13:J14)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Imobilizado</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Pagamento de R$ 38.000 a fornecedores</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>-38000</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Contas a Pagar</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
         <v>-38000</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="8">
-        <f>IF(COUNT(C13:C14,E13:E14,G13:G14)=0,"",IF(SUM(C13:C14)-SUM(E13:E14)-SUM(G13:G14)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="6">
+        <f>IF(COUNT(D15:D16,G15:G16,J15:J16)=0,"",IF(SUM(D15:D16)-SUM(G15:G16)-SUM(J15:J16)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="n">
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Pagamento à vista de despesas de vendas e administrativas: R$ 14.000</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
         <v>-14000</v>
       </c>
-      <c r="H15" s="8">
-        <f>IF(COUNT(C15:C16,E15:E16,G15:G16)=0,"",IF(SUM(C15:C16)-SUM(E15:E16)-SUM(G15:G16)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="K17" s="6">
+        <f>IF(COUNT(D17:D18,G17:G18,J17:J18)=0,"",IF(SUM(D17:D18)-SUM(G17:G18)-SUM(J17:J18)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="n">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Aporte adicional de capital dos sócios: R$ 20.000 em dinheiro</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Capital Social</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
         <v>20000</v>
       </c>
-      <c r="H17" s="8">
-        <f>IF(COUNT(C17:C18,E17:E18,G17:G18)=0,"",IF(SUM(C17:C18)-SUM(E17:E18)-SUM(G17:G18)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="K19" s="6">
+        <f>IF(COUNT(D19:D20,G19:G20,J19:J20)=0,"",IF(SUM(D19:D20)-SUM(G19:G20)-SUM(J19:J20)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Distribuição de dividendos de R$ 5.000 em dinheiro</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
         <v>-5000</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Lucros Acumulados</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
         <v>-5000</v>
       </c>
-      <c r="H19" s="8">
-        <f>IF(COUNT(C19:C20,E19:E20,G19:G20)=0,"",IF(SUM(C19:C20)-SUM(E19:E20)-SUM(G19:G20)=0,"✔","✗"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="K21" s="6">
+        <f>IF(COUNT(D21:D22,G21:G22,J21:J22)=0,"",IF(SUM(D21:D22)-SUM(G21:G22)-SUM(J21:J22)=0,"✔","✗"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="H9:H10"/>
+  <mergeCells count="27">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K21:K22"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="K10:K12"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A8:A9"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K17:K18"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="B21:B22"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Caixa,Contas a Receber,Estoque,Imobilizado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Contas a Pagar"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Capital Social,Lucros Acumulados"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ContabilidadeFinanceira/Treinos/Ex3_ValeVerde.xlsx
+++ b/ContabilidadeFinanceira/Treinos/Ex3_ValeVerde.xlsx
@@ -1034,7 +1034,7 @@
       <c r="J22" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="K21:K22"/>
     <mergeCell ref="B17:B18"/>
@@ -1048,6 +1048,7 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="K17:K18"/>
@@ -1106,7 +1107,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Distribuidora Vale Verde  |  Mês 2  |  valores em R$</t>
+          <t>Distribuidora Vale Verde</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
@@ -1116,6 +1117,11 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Mês 2  |  valores em R$</t>
+        </is>
+      </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Recebimento de R$ 12.000 de clientes, referente a vendas do </t>
@@ -2197,6 +2203,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2229,7 +2238,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Distribuidora Vale Verde  |  Mês 2  |  valores em R$</t>
+          <t>Distribuidora Vale Verde</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
@@ -2239,6 +2248,11 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Mês 2  |  valores em R$</t>
+        </is>
+      </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Recebimento de R$ 12.000 de clientes, referente a vendas do </t>
@@ -3306,6 +3320,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3940,7 +3957,7 @@
       <c r="J22" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="K21:K22"/>
     <mergeCell ref="B17:B18"/>
@@ -3954,6 +3971,7 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="K17:K18"/>
